--- a/liaisons_Super_Constellation/Reseau_Irish_Airlines_L1049_sourced.xlsx
+++ b/liaisons_Super_Constellation/Reseau_Irish_Airlines_L1049_sourced.xlsx
@@ -593,7 +593,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Notes historiques :</v>
+        <v>Notes :</v>
       </c>
       <c r="B7" t="str">
         <v/>
@@ -754,6 +754,33 @@
     <row r="12">
       <c r="A12" t="str">
         <v>[R] Vols retour ajoutés automatiquement (itinéraire miroir, horaires reconstitués).</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
